--- a/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T09:33:49+00:00</t>
+    <t>2026-03-30T15:11:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T15:11:58+00:00</t>
+    <t>2026-03-31T07:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T07:16:03+00:00</t>
+    <t>2026-04-01T07:43:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T07:43:12+00:00</t>
+    <t>2026-04-02T07:21:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T07:21:27+00:00</t>
+    <t>2026-04-02T12:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T12:41:19+00:00</t>
+    <t>2026-04-07T08:23:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T08:23:13+00:00</t>
+    <t>2026-04-15T13:29:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T13:29:57+00:00</t>
+    <t>2026-04-15T15:41:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-15T15:41:19+00:00</t>
+    <t>2026-04-20T15:11:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4861,7 +4861,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>157</v>
       </c>
@@ -4880,7 +4880,7 @@
         <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>74</v>

--- a/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:11:12+00:00</t>
+    <t>2026-04-23T15:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T15:25:59+00:00</t>
+    <t>2026-05-06T07:44:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T07:44:21+00:00</t>
+    <t>2026-05-13T14:53:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:53:03+00:00</t>
+    <t>2026-05-15T08:08:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:35:10+00:00</t>
+    <t>2026-06-29T12:53:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$246</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$247</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7643" uniqueCount="621">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7673" uniqueCount="624">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:53:00+00:00</t>
+    <t>2026-06-29T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -663,6 +663,10 @@
     <t>ED.thumbnail</t>
   </si>
   <si>
+    <t xml:space="preserve">ED-1:Thumbnails cannot contain their own thumbnails {thumbnail.empty()}
+</t>
+  </si>
+  <si>
     <t>Supply.statusCode</t>
   </si>
   <si>
@@ -1140,6 +1144,12 @@
   </si>
   <si>
     <t>ParticipantRole.code</t>
+  </si>
+  <si>
+    <t>Supply.participant.participantRole.sdtcSpecialty</t>
+  </si>
+  <si>
+    <t>ParticipantRole.sdtcSpecialty</t>
   </si>
   <si>
     <t>Supply.participant.participantRole.addr</t>
@@ -2255,7 +2265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK246"/>
+  <dimension ref="A1:AK247"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="71.953125" customWidth="true" bestFit="true"/>
@@ -6176,7 +6186,7 @@
         <v>74</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>74</v>
+        <v>210</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>74</v>
@@ -6184,10 +6194,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6213,10 +6223,10 @@
         <v>91</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6247,7 +6257,7 @@
       </c>
       <c r="Y39" s="2"/>
       <c r="Z39" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>74</v>
@@ -6265,7 +6275,7 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6285,10 +6295,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6311,13 +6321,13 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6368,7 +6378,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6388,10 +6398,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6414,7 +6424,7 @@
         <v>74</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
@@ -6447,7 +6457,7 @@
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>74</v>
@@ -6465,7 +6475,7 @@
         <v>74</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6485,10 +6495,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6511,13 +6521,13 @@
         <v>74</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6568,7 +6578,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -6588,10 +6598,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6614,7 +6624,7 @@
         <v>74</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
@@ -6667,7 +6677,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6687,10 +6697,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6713,10 +6723,10 @@
         <v>74</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
@@ -6768,7 +6778,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6788,10 +6798,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6814,13 +6824,13 @@
         <v>74</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6871,7 +6881,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -6891,10 +6901,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6917,7 +6927,7 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
@@ -6970,7 +6980,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6990,10 +7000,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7091,10 +7101,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7192,10 +7202,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7293,10 +7303,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7394,10 +7404,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7497,10 +7507,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7600,10 +7610,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7703,10 +7713,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7806,10 +7816,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7907,10 +7917,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7944,7 +7954,7 @@
       </c>
       <c r="Q56" s="2"/>
       <c r="R56" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="S56" t="s" s="2">
         <v>74</v>
@@ -7966,7 +7976,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>74</v>
@@ -7984,7 +7994,7 @@
         <v>74</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8004,10 +8014,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8030,7 +8040,7 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
@@ -8083,7 +8093,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>75</v>
@@ -8103,10 +8113,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8129,7 +8139,7 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
@@ -8182,7 +8192,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8202,10 +8212,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8228,7 +8238,7 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -8281,7 +8291,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8301,10 +8311,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8327,13 +8337,13 @@
         <v>74</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8384,7 +8394,7 @@
         <v>74</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8404,10 +8414,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8505,10 +8515,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8606,10 +8616,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8707,10 +8717,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8808,10 +8818,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8911,10 +8921,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9014,10 +9024,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9117,10 +9127,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9220,10 +9230,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9321,10 +9331,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9358,7 +9368,7 @@
       </c>
       <c r="Q70" s="2"/>
       <c r="R70" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="S70" t="s" s="2">
         <v>74</v>
@@ -9380,7 +9390,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>74</v>
@@ -9398,7 +9408,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -9418,10 +9428,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9444,7 +9454,7 @@
         <v>74</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
@@ -9497,7 +9507,7 @@
         <v>74</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -9517,10 +9527,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9543,7 +9553,7 @@
         <v>74</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
@@ -9596,7 +9606,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -9616,10 +9626,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9660,7 +9670,7 @@
         <v>74</v>
       </c>
       <c r="S73" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="T73" t="s" s="2">
         <v>74</v>
@@ -9717,10 +9727,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9743,11 +9753,11 @@
         <v>74</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9798,7 +9808,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -9818,10 +9828,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9848,12 +9858,12 @@
       </c>
       <c r="L75" s="2"/>
       <c r="M75" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
@@ -9879,7 +9889,7 @@
       </c>
       <c r="Y75" s="2"/>
       <c r="Z75" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>74</v>
@@ -9897,7 +9907,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9917,17 +9927,17 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F76" t="s" s="2">
         <v>80</v>
@@ -9945,11 +9955,11 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -10000,7 +10010,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -10020,17 +10030,17 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E77" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F77" t="s" s="2">
         <v>80</v>
@@ -10048,11 +10058,11 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10103,7 +10113,7 @@
         <v>74</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -10123,17 +10133,17 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E78" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F78" t="s" s="2">
         <v>80</v>
@@ -10151,11 +10161,11 @@
         <v>74</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -10206,7 +10216,7 @@
         <v>74</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -10226,17 +10236,17 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E79" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="F79" t="s" s="2">
         <v>80</v>
@@ -10254,11 +10264,11 @@
         <v>74</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -10309,7 +10319,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -10329,10 +10339,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10355,7 +10365,7 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -10408,7 +10418,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -10428,10 +10438,10 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10454,7 +10464,7 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -10507,7 +10517,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>75</v>
@@ -10527,10 +10537,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10553,7 +10563,7 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
@@ -10606,7 +10616,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -10626,10 +10636,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10652,7 +10662,7 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -10705,7 +10715,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -10725,10 +10735,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10751,13 +10761,13 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -10808,7 +10818,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -10828,10 +10838,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -10929,10 +10939,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11030,10 +11040,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11131,10 +11141,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11232,10 +11242,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11335,10 +11345,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11438,10 +11448,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11541,10 +11551,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11644,10 +11654,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11745,10 +11755,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11785,7 +11795,7 @@
         <v>74</v>
       </c>
       <c r="S94" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="T94" t="s" s="2">
         <v>74</v>
@@ -11804,7 +11814,7 @@
       </c>
       <c r="Y94" s="2"/>
       <c r="Z94" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>74</v>
@@ -11822,7 +11832,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>
@@ -11842,10 +11852,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11879,7 +11889,7 @@
       </c>
       <c r="Q95" s="2"/>
       <c r="R95" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="S95" t="s" s="2">
         <v>74</v>
@@ -11901,7 +11911,7 @@
       </c>
       <c r="Y95" s="2"/>
       <c r="Z95" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>74</v>
@@ -11919,7 +11929,7 @@
         <v>74</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -11939,10 +11949,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -11965,7 +11975,7 @@
         <v>74</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
@@ -12018,7 +12028,7 @@
         <v>74</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -12038,10 +12048,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12064,7 +12074,7 @@
         <v>74</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
@@ -12117,7 +12127,7 @@
         <v>74</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -12137,10 +12147,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12163,7 +12173,7 @@
         <v>74</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" s="2"/>
@@ -12216,7 +12226,7 @@
         <v>74</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -12236,10 +12246,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12262,7 +12272,7 @@
         <v>74</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
@@ -12315,7 +12325,7 @@
         <v>74</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>75</v>
@@ -12335,10 +12345,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12436,10 +12446,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12537,10 +12547,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12638,10 +12648,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -12739,10 +12749,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12842,10 +12852,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12945,10 +12955,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13048,10 +13058,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13151,10 +13161,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13252,10 +13262,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13285,14 +13295,14 @@
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q109" s="2"/>
       <c r="R109" t="s" s="2">
         <v>74</v>
       </c>
       <c r="S109" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="T109" t="s" s="2">
         <v>74</v>
@@ -13311,7 +13321,7 @@
       </c>
       <c r="Y109" s="2"/>
       <c r="Z109" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>74</v>
@@ -13329,7 +13339,7 @@
         <v>74</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -13349,10 +13359,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13378,10 +13388,10 @@
         <v>95</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -13432,7 +13442,7 @@
         <v>74</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -13452,10 +13462,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13478,7 +13488,7 @@
         <v>74</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -13531,7 +13541,7 @@
         <v>74</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
@@ -13551,10 +13561,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13577,7 +13587,7 @@
         <v>74</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -13610,7 +13620,7 @@
       </c>
       <c r="Y112" s="2"/>
       <c r="Z112" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>74</v>
@@ -13628,7 +13638,7 @@
         <v>74</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -13648,10 +13658,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13674,7 +13684,7 @@
         <v>74</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>364</v>
+        <v>219</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
@@ -13773,7 +13783,7 @@
         <v>74</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>202</v>
+        <v>367</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -13826,7 +13836,7 @@
         <v>74</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>80</v>
@@ -13846,10 +13856,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -13857,10 +13867,10 @@
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G115" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H115" t="s" s="2">
         <v>74</v>
@@ -13872,14 +13882,10 @@
         <v>74</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="L115" s="2"/>
+      <c r="M115" s="2"/>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -13929,13 +13935,13 @@
         <v>74</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH115" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI115" t="s" s="2">
         <v>74</v>
@@ -13949,20 +13955,18 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E116" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G116" t="s" s="2">
         <v>75</v>
@@ -13977,11 +13981,13 @@
         <v>74</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L116" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>373</v>
+      </c>
       <c r="M116" t="s" s="2">
-        <v>86</v>
+        <v>373</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -14008,11 +14014,13 @@
         <v>74</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y116" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z116" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>74</v>
@@ -14030,7 +14038,7 @@
         <v>74</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>89</v>
+        <v>374</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -14050,21 +14058,23 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E117" s="2"/>
+      <c r="E117" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G117" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H117" t="s" s="2">
         <v>74</v>
@@ -14076,11 +14086,11 @@
         <v>74</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -14107,13 +14117,11 @@
         <v>74</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y117" s="2"/>
       <c r="Z117" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>74</v>
@@ -14131,13 +14139,13 @@
         <v>74</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH117" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI117" t="s" s="2">
         <v>74</v>
@@ -14151,10 +14159,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14165,7 +14173,7 @@
         <v>80</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>74</v>
@@ -14177,11 +14185,11 @@
         <v>74</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -14232,19 +14240,19 @@
         <v>74</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ118" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK118" t="s" s="2">
         <v>74</v>
@@ -14252,18 +14260,16 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E119" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
         <v>80</v>
       </c>
@@ -14280,11 +14286,11 @@
         <v>74</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L119" s="2"/>
       <c r="M119" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -14311,11 +14317,13 @@
         <v>74</v>
       </c>
       <c r="X119" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y119" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z119" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>74</v>
@@ -14333,7 +14341,7 @@
         <v>74</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -14345,7 +14353,7 @@
         <v>74</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>74</v>
@@ -14353,17 +14361,17 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E120" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F120" t="s" s="2">
         <v>80</v>
@@ -14381,11 +14389,11 @@
         <v>74</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -14412,13 +14420,11 @@
         <v>74</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y120" s="2"/>
       <c r="Z120" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>74</v>
@@ -14436,7 +14442,7 @@
         <v>74</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -14456,17 +14462,17 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E121" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F121" t="s" s="2">
         <v>80</v>
@@ -14484,11 +14490,11 @@
         <v>74</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L121" s="2"/>
       <c r="M121" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -14539,7 +14545,7 @@
         <v>74</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -14559,20 +14565,20 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E122" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F122" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G122" t="s" s="2">
         <v>75</v>
@@ -14587,11 +14593,11 @@
         <v>74</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L122" s="2"/>
       <c r="M122" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -14600,7 +14606,7 @@
       </c>
       <c r="Q122" s="2"/>
       <c r="R122" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S122" t="s" s="2">
         <v>74</v>
@@ -14642,7 +14648,7 @@
         <v>74</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -14662,17 +14668,17 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E123" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F123" t="s" s="2">
         <v>75</v>
@@ -14690,11 +14696,11 @@
         <v>74</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L123" s="2"/>
       <c r="M123" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -14703,7 +14709,7 @@
       </c>
       <c r="Q123" s="2"/>
       <c r="R123" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S123" t="s" s="2">
         <v>74</v>
@@ -14745,7 +14751,7 @@
         <v>74</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>80</v>
@@ -14765,21 +14771,23 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E124" s="2"/>
+      <c r="E124" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F124" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>74</v>
@@ -14791,11 +14799,11 @@
         <v>74</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L124" s="2"/>
       <c r="M124" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -14846,13 +14854,13 @@
         <v>74</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>74</v>
@@ -14864,12 +14872,12 @@
         <v>74</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -14880,10 +14888,10 @@
         <v>80</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>74</v>
@@ -14892,21 +14900,23 @@
         <v>74</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L125" s="2"/>
-      <c r="M125" s="2"/>
+      <c r="M125" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
-        <v>323</v>
+        <v>74</v>
       </c>
       <c r="Q125" s="2"/>
       <c r="R125" t="s" s="2">
         <v>74</v>
       </c>
       <c r="S125" t="s" s="2">
-        <v>323</v>
+        <v>74</v>
       </c>
       <c r="T125" t="s" s="2">
         <v>74</v>
@@ -14921,11 +14931,13 @@
         <v>74</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y125" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z125" t="s" s="2">
-        <v>382</v>
+        <v>74</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>74</v>
@@ -14943,13 +14955,13 @@
         <v>74</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>383</v>
+        <v>125</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>74</v>
@@ -14961,7 +14973,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
         <v>384</v>
       </c>
@@ -14980,7 +14992,7 @@
         <v>75</v>
       </c>
       <c r="H126" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I126" t="s" s="2">
         <v>74</v>
@@ -14996,14 +15008,14 @@
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
-        <v>74</v>
+        <v>324</v>
       </c>
       <c r="Q126" s="2"/>
       <c r="R126" t="s" s="2">
-        <v>385</v>
+        <v>74</v>
       </c>
       <c r="S126" t="s" s="2">
-        <v>74</v>
+        <v>324</v>
       </c>
       <c r="T126" t="s" s="2">
         <v>74</v>
@@ -15022,48 +15034,48 @@
       </c>
       <c r="Y126" s="2"/>
       <c r="Z126" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="AA126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF126" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AA126" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF126" t="s" s="2">
+      <c r="AG126" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH126" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ126" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK126" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="127" hidden="true">
+      <c r="A127" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AG126" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s" s="2">
-        <v>388</v>
-      </c>
       <c r="B127" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15071,13 +15083,13 @@
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G127" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>74</v>
@@ -15086,14 +15098,10 @@
         <v>74</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="L127" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="M127" t="s" s="2">
-        <v>390</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="L127" s="2"/>
+      <c r="M127" s="2"/>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
@@ -15101,7 +15109,7 @@
       </c>
       <c r="Q127" s="2"/>
       <c r="R127" t="s" s="2">
-        <v>74</v>
+        <v>388</v>
       </c>
       <c r="S127" t="s" s="2">
         <v>74</v>
@@ -15119,68 +15127,66 @@
         <v>74</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>162</v>
+        <v>87</v>
       </c>
       <c r="Y127" s="2"/>
       <c r="Z127" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AA127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF127" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AG127" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH127" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ127" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK127" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AA127" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="128" hidden="true">
-      <c r="A128" t="s" s="2">
-        <v>393</v>
-      </c>
       <c r="B128" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E128" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G128" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H128" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I128" t="s" s="2">
         <v>74</v>
@@ -15189,11 +15195,13 @@
         <v>74</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L128" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>392</v>
+      </c>
       <c r="M128" t="s" s="2">
-        <v>86</v>
+        <v>393</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -15220,11 +15228,11 @@
         <v>74</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>87</v>
+        <v>162</v>
       </c>
       <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
-        <v>88</v>
+        <v>394</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>74</v>
@@ -15242,7 +15250,7 @@
         <v>74</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>89</v>
+        <v>395</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -15262,17 +15270,17 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E129" t="s" s="2">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="F129" t="s" s="2">
         <v>80</v>
@@ -15294,7 +15302,7 @@
       </c>
       <c r="L129" s="2"/>
       <c r="M129" t="s" s="2">
-        <v>395</v>
+        <v>86</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -15321,13 +15329,11 @@
         <v>74</v>
       </c>
       <c r="X129" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y129" s="2"/>
       <c r="Z129" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA129" t="s" s="2">
         <v>74</v>
@@ -15345,7 +15351,7 @@
         <v>74</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>396</v>
+        <v>89</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>80</v>
@@ -15375,7 +15381,7 @@
         <v>74</v>
       </c>
       <c r="E130" t="s" s="2">
-        <v>398</v>
+        <v>62</v>
       </c>
       <c r="F130" t="s" s="2">
         <v>80</v>
@@ -15393,11 +15399,11 @@
         <v>74</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>112</v>
+        <v>85</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -15448,7 +15454,7 @@
         <v>74</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>80</v>
@@ -15468,17 +15474,17 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E131" t="s" s="2">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F131" t="s" s="2">
         <v>80</v>
@@ -15496,11 +15502,11 @@
         <v>74</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" t="s" s="2">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -15551,7 +15557,7 @@
         <v>74</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -15571,17 +15577,17 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E132" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F132" t="s" s="2">
         <v>80</v>
@@ -15603,7 +15609,7 @@
       </c>
       <c r="L132" s="2"/>
       <c r="M132" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -15654,7 +15660,7 @@
         <v>74</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>80</v>
@@ -15674,17 +15680,17 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E133" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="F133" t="s" s="2">
         <v>80</v>
@@ -15706,7 +15712,7 @@
       </c>
       <c r="L133" s="2"/>
       <c r="M133" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -15757,7 +15763,7 @@
         <v>74</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -15777,16 +15783,18 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E134" s="2"/>
+      <c r="E134" t="s" s="2">
+        <v>413</v>
+      </c>
       <c r="F134" t="s" s="2">
         <v>80</v>
       </c>
@@ -15803,11 +15811,11 @@
         <v>74</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>414</v>
+        <v>102</v>
       </c>
       <c r="L134" s="2"/>
       <c r="M134" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -15858,7 +15866,7 @@
         <v>74</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>80</v>
@@ -15878,10 +15886,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -15904,7 +15912,7 @@
         <v>74</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>102</v>
+        <v>417</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" t="s" s="2">
@@ -15988,9 +15996,7 @@
       <c r="D136" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E136" t="s" s="2">
-        <v>421</v>
-      </c>
+      <c r="E136" s="2"/>
       <c r="F136" t="s" s="2">
         <v>80</v>
       </c>
@@ -16007,11 +16013,11 @@
         <v>74</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -16062,7 +16068,7 @@
         <v>74</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>80</v>
@@ -16082,23 +16088,23 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E137" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F137" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G137" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H137" t="s" s="2">
         <v>74</v>
@@ -16110,11 +16116,11 @@
         <v>74</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>426</v>
+        <v>165</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" t="s" s="2">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -16165,13 +16171,13 @@
         <v>74</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH137" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI137" t="s" s="2">
         <v>74</v>
@@ -16183,43 +16189,41 @@
         <v>74</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E138" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="F138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G138" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H138" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I138" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J138" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K138" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="L138" s="2"/>
+      <c r="M138" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="F138" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G138" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H138" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="I138" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J138" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K138" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="L138" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="M138" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -16270,7 +16274,7 @@
         <v>74</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>80</v>
@@ -16288,26 +16292,28 @@
         <v>74</v>
       </c>
     </row>
-    <row r="139" hidden="true">
+    <row r="139">
       <c r="A139" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E139" s="2"/>
+      <c r="E139" t="s" s="2">
+        <v>433</v>
+      </c>
       <c r="F139" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G139" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H139" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I139" t="s" s="2">
         <v>74</v>
@@ -16316,10 +16322,14 @@
         <v>74</v>
       </c>
       <c r="K139" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="L139" s="2"/>
-      <c r="M139" s="2"/>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
@@ -16345,35 +16355,37 @@
         <v>74</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="Y139" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y139" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z139" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA139" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB139" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC139" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD139" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE139" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF139" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="AA139" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>437</v>
-      </c>
       <c r="AG139" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH139" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI139" t="s" s="2">
         <v>74</v>
@@ -16387,10 +16399,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16413,7 +16425,7 @@
         <v>74</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
@@ -16510,7 +16522,7 @@
         <v>74</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="L141" s="2"/>
       <c r="M141" s="2"/>
@@ -16539,13 +16551,11 @@
         <v>74</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="Y141" s="2"/>
       <c r="Z141" t="s" s="2">
-        <v>74</v>
+        <v>442</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>74</v>
@@ -16696,10 +16706,10 @@
         <v>80</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H143" t="s" s="2">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="I143" t="s" s="2">
         <v>74</v>
@@ -16749,23 +16759,25 @@
         <v>74</v>
       </c>
       <c r="AB143" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC143" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD143" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE143" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF143" t="s" s="2">
         <v>449</v>
       </c>
-      <c r="AC143" s="2"/>
-      <c r="AD143" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE143" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AF143" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AG143" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>74</v>
@@ -16782,11 +16794,9 @@
         <v>450</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C144" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>450</v>
+      </c>
+      <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
         <v>74</v>
       </c>
@@ -16795,10 +16805,10 @@
         <v>80</v>
       </c>
       <c r="G144" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H144" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I144" t="s" s="2">
         <v>74</v>
@@ -16807,11 +16817,9 @@
         <v>74</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="L144" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="L144" s="2"/>
       <c r="M144" s="2"/>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -16850,19 +16858,17 @@
         <v>74</v>
       </c>
       <c r="AB144" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC144" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="AC144" s="2"/>
       <c r="AD144" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE144" t="s" s="2">
-        <v>74</v>
+        <v>124</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>80</v>
@@ -16885,15 +16891,15 @@
         <v>453</v>
       </c>
       <c r="B145" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="C145" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E145" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
         <v>80</v>
       </c>
@@ -16910,12 +16916,12 @@
         <v>74</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L145" s="2"/>
-      <c r="M145" t="s" s="2">
-        <v>86</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="L145" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M145" s="2"/>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -16941,11 +16947,13 @@
         <v>74</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y145" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y145" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z145" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>74</v>
@@ -16963,13 +16971,13 @@
         <v>74</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>89</v>
+        <v>450</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>74</v>
@@ -16983,21 +16991,23 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E146" s="2"/>
+      <c r="E146" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F146" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G146" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H146" t="s" s="2">
         <v>74</v>
@@ -17009,11 +17019,11 @@
         <v>74</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L146" s="2"/>
       <c r="M146" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" s="2"/>
@@ -17040,13 +17050,11 @@
         <v>74</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y146" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y146" s="2"/>
       <c r="Z146" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>74</v>
@@ -17064,13 +17072,13 @@
         <v>74</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH146" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI146" t="s" s="2">
         <v>74</v>
@@ -17084,10 +17092,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17098,7 +17106,7 @@
         <v>80</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>74</v>
@@ -17110,11 +17118,11 @@
         <v>74</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L147" s="2"/>
       <c r="M147" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -17165,19 +17173,19 @@
         <v>74</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ147" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK147" t="s" s="2">
         <v>74</v>
@@ -17185,18 +17193,16 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E148" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E148" s="2"/>
       <c r="F148" t="s" s="2">
         <v>80</v>
       </c>
@@ -17213,11 +17219,11 @@
         <v>74</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L148" s="2"/>
       <c r="M148" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
@@ -17244,11 +17250,13 @@
         <v>74</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y148" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y148" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z148" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>74</v>
@@ -17266,7 +17274,7 @@
         <v>74</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>80</v>
@@ -17278,7 +17286,7 @@
         <v>74</v>
       </c>
       <c r="AJ148" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK148" t="s" s="2">
         <v>74</v>
@@ -17286,17 +17294,17 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E149" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F149" t="s" s="2">
         <v>80</v>
@@ -17314,11 +17322,11 @@
         <v>74</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L149" s="2"/>
       <c r="M149" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -17345,13 +17353,11 @@
         <v>74</v>
       </c>
       <c r="X149" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y149" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y149" s="2"/>
       <c r="Z149" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA149" t="s" s="2">
         <v>74</v>
@@ -17369,7 +17375,7 @@
         <v>74</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>80</v>
@@ -17389,17 +17395,17 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E150" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F150" t="s" s="2">
         <v>80</v>
@@ -17417,11 +17423,11 @@
         <v>74</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L150" s="2"/>
       <c r="M150" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
@@ -17472,7 +17478,7 @@
         <v>74</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>80</v>
@@ -17492,20 +17498,20 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E151" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F151" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G151" t="s" s="2">
         <v>75</v>
@@ -17520,11 +17526,11 @@
         <v>74</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L151" s="2"/>
       <c r="M151" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -17533,7 +17539,7 @@
       </c>
       <c r="Q151" s="2"/>
       <c r="R151" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S151" t="s" s="2">
         <v>74</v>
@@ -17575,7 +17581,7 @@
         <v>74</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>80</v>
@@ -17595,17 +17601,17 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E152" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F152" t="s" s="2">
         <v>75</v>
@@ -17623,11 +17629,11 @@
         <v>74</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L152" s="2"/>
       <c r="M152" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -17636,7 +17642,7 @@
       </c>
       <c r="Q152" s="2"/>
       <c r="R152" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S152" t="s" s="2">
         <v>74</v>
@@ -17678,7 +17684,7 @@
         <v>74</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>80</v>
@@ -17698,21 +17704,23 @@
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E153" s="2"/>
+      <c r="E153" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F153" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G153" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H153" t="s" s="2">
         <v>74</v>
@@ -17724,11 +17732,11 @@
         <v>74</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L153" s="2"/>
       <c r="M153" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -17779,13 +17787,13 @@
         <v>74</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH153" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI153" t="s" s="2">
         <v>74</v>
@@ -17799,10 +17807,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -17810,10 +17818,10 @@
       </c>
       <c r="E154" s="2"/>
       <c r="F154" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G154" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H154" t="s" s="2">
         <v>74</v>
@@ -17825,10 +17833,12 @@
         <v>74</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L154" s="2"/>
-      <c r="M154" s="2"/>
+      <c r="M154" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
       <c r="P154" t="s" s="2">
@@ -17839,7 +17849,7 @@
         <v>74</v>
       </c>
       <c r="S154" t="s" s="2">
-        <v>473</v>
+        <v>74</v>
       </c>
       <c r="T154" t="s" s="2">
         <v>74</v>
@@ -17854,11 +17864,13 @@
         <v>74</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y154" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y154" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z154" t="s" s="2">
-        <v>474</v>
+        <v>74</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>74</v>
@@ -17876,13 +17888,13 @@
         <v>74</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>475</v>
+        <v>125</v>
       </c>
       <c r="AG154" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH154" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI154" t="s" s="2">
         <v>74</v>
@@ -17896,10 +17908,10 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -17907,7 +17919,7 @@
       </c>
       <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G155" t="s" s="2">
         <v>75</v>
@@ -17922,12 +17934,10 @@
         <v>74</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L155" s="2"/>
-      <c r="M155" t="s" s="2">
-        <v>478</v>
-      </c>
+      <c r="M155" s="2"/>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -17938,7 +17948,7 @@
         <v>74</v>
       </c>
       <c r="S155" t="s" s="2">
-        <v>74</v>
+        <v>476</v>
       </c>
       <c r="T155" t="s" s="2">
         <v>74</v>
@@ -17953,13 +17963,11 @@
         <v>74</v>
       </c>
       <c r="X155" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y155" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y155" s="2"/>
       <c r="Z155" t="s" s="2">
-        <v>74</v>
+        <v>477</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>74</v>
@@ -17977,10 +17985,10 @@
         <v>74</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AG155" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH155" t="s" s="2">
         <v>75</v>
@@ -17997,10 +18005,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B156" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="B156" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -18027,12 +18035,12 @@
       </c>
       <c r="L156" s="2"/>
       <c r="M156" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
       <c r="P156" t="s" s="2">
-        <v>483</v>
+        <v>74</v>
       </c>
       <c r="Q156" s="2"/>
       <c r="R156" t="s" s="2">
@@ -18078,7 +18086,7 @@
         <v>74</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>80</v>
@@ -18098,10 +18106,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -18127,11 +18135,13 @@
         <v>107</v>
       </c>
       <c r="L157" s="2"/>
-      <c r="M157" s="2"/>
+      <c r="M157" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
       <c r="P157" t="s" s="2">
-        <v>74</v>
+        <v>486</v>
       </c>
       <c r="Q157" s="2"/>
       <c r="R157" t="s" s="2">
@@ -18223,7 +18233,7 @@
         <v>74</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>490</v>
+        <v>107</v>
       </c>
       <c r="L158" s="2"/>
       <c r="M158" s="2"/>
@@ -18276,7 +18286,7 @@
         <v>74</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>80</v>
@@ -18296,10 +18306,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="B159" t="s" s="2">
         <v>492</v>
-      </c>
-      <c r="B159" t="s" s="2">
-        <v>493</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18322,7 +18332,7 @@
         <v>74</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>224</v>
+        <v>493</v>
       </c>
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
@@ -18421,7 +18431,7 @@
         <v>74</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>497</v>
+        <v>225</v>
       </c>
       <c r="L160" s="2"/>
       <c r="M160" s="2"/>
@@ -18474,7 +18484,7 @@
         <v>74</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>80</v>
@@ -18494,10 +18504,10 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B161" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="B161" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -18520,7 +18530,7 @@
         <v>74</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
@@ -18573,7 +18583,7 @@
         <v>74</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>80</v>
@@ -18593,10 +18603,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="B162" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="B162" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18619,7 +18629,7 @@
         <v>74</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
@@ -18672,7 +18682,7 @@
         <v>74</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>80</v>
@@ -18692,10 +18702,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="B163" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="B163" t="s" s="2">
-        <v>508</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -18718,7 +18728,7 @@
         <v>74</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L163" s="2"/>
       <c r="M163" s="2"/>
@@ -18771,7 +18781,7 @@
         <v>74</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>80</v>
@@ -18791,10 +18801,10 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B164" t="s" s="2">
         <v>511</v>
-      </c>
-      <c r="B164" t="s" s="2">
-        <v>512</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -18817,7 +18827,7 @@
         <v>74</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L164" s="2"/>
       <c r="M164" s="2"/>
@@ -18870,7 +18880,7 @@
         <v>74</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>80</v>
@@ -18890,10 +18900,10 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="B165" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="B165" t="s" s="2">
-        <v>516</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -18916,7 +18926,7 @@
         <v>74</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="L165" s="2"/>
       <c r="M165" s="2"/>
@@ -18969,7 +18979,7 @@
         <v>74</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>80</v>
@@ -18989,10 +18999,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B166" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="B166" t="s" s="2">
-        <v>520</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -19015,7 +19025,7 @@
         <v>74</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
@@ -19068,7 +19078,7 @@
         <v>74</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>80</v>
@@ -19088,10 +19098,10 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="B167" t="s" s="2">
         <v>523</v>
-      </c>
-      <c r="B167" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -19114,7 +19124,7 @@
         <v>74</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
@@ -19167,7 +19177,7 @@
         <v>74</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>80</v>
@@ -19187,10 +19197,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B168" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="B168" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -19213,7 +19223,7 @@
         <v>74</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
@@ -19266,7 +19276,7 @@
         <v>74</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>80</v>
@@ -19286,14 +19296,12 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B169" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="B169" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C169" t="s" s="2">
-        <v>532</v>
-      </c>
+      <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
         <v>74</v>
       </c>
@@ -19314,11 +19322,9 @@
         <v>74</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="L169" t="s" s="2">
-        <v>533</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="L169" s="2"/>
       <c r="M169" s="2"/>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -19369,13 +19375,13 @@
         <v>74</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>447</v>
+        <v>533</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI169" t="s" s="2">
         <v>74</v>
@@ -19392,15 +19398,15 @@
         <v>534</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C170" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="C170" t="s" s="2">
+        <v>535</v>
+      </c>
       <c r="D170" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E170" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
         <v>80</v>
       </c>
@@ -19417,12 +19423,12 @@
         <v>74</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L170" s="2"/>
-      <c r="M170" t="s" s="2">
-        <v>86</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="L170" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M170" s="2"/>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
@@ -19448,11 +19454,13 @@
         <v>74</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y170" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y170" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z170" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>74</v>
@@ -19470,13 +19478,13 @@
         <v>74</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>89</v>
+        <v>450</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH170" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI170" t="s" s="2">
         <v>74</v>
@@ -19490,21 +19498,23 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E171" s="2"/>
+      <c r="E171" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F171" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H171" t="s" s="2">
         <v>74</v>
@@ -19516,11 +19526,11 @@
         <v>74</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L171" s="2"/>
       <c r="M171" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -19547,13 +19557,11 @@
         <v>74</v>
       </c>
       <c r="X171" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y171" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y171" s="2"/>
       <c r="Z171" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA171" t="s" s="2">
         <v>74</v>
@@ -19571,13 +19579,13 @@
         <v>74</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH171" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI171" t="s" s="2">
         <v>74</v>
@@ -19591,10 +19599,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19605,7 +19613,7 @@
         <v>80</v>
       </c>
       <c r="G172" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H172" t="s" s="2">
         <v>74</v>
@@ -19617,11 +19625,11 @@
         <v>74</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L172" s="2"/>
       <c r="M172" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -19672,19 +19680,19 @@
         <v>74</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH172" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI172" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ172" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK172" t="s" s="2">
         <v>74</v>
@@ -19692,18 +19700,16 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E173" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E173" s="2"/>
       <c r="F173" t="s" s="2">
         <v>80</v>
       </c>
@@ -19720,11 +19726,11 @@
         <v>74</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L173" s="2"/>
       <c r="M173" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" s="2"/>
@@ -19751,11 +19757,13 @@
         <v>74</v>
       </c>
       <c r="X173" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y173" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y173" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z173" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>74</v>
@@ -19773,7 +19781,7 @@
         <v>74</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>80</v>
@@ -19785,7 +19793,7 @@
         <v>74</v>
       </c>
       <c r="AJ173" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK173" t="s" s="2">
         <v>74</v>
@@ -19793,17 +19801,17 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E174" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F174" t="s" s="2">
         <v>80</v>
@@ -19821,11 +19829,11 @@
         <v>74</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L174" s="2"/>
       <c r="M174" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N174" s="2"/>
       <c r="O174" s="2"/>
@@ -19852,13 +19860,11 @@
         <v>74</v>
       </c>
       <c r="X174" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y174" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y174" s="2"/>
       <c r="Z174" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>74</v>
@@ -19876,7 +19882,7 @@
         <v>74</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>80</v>
@@ -19896,17 +19902,17 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E175" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F175" t="s" s="2">
         <v>80</v>
@@ -19924,11 +19930,11 @@
         <v>74</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L175" s="2"/>
       <c r="M175" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -19979,7 +19985,7 @@
         <v>74</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>80</v>
@@ -19999,20 +20005,20 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E176" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F176" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G176" t="s" s="2">
         <v>75</v>
@@ -20027,11 +20033,11 @@
         <v>74</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L176" s="2"/>
       <c r="M176" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -20040,7 +20046,7 @@
       </c>
       <c r="Q176" s="2"/>
       <c r="R176" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S176" t="s" s="2">
         <v>74</v>
@@ -20082,7 +20088,7 @@
         <v>74</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>80</v>
@@ -20102,17 +20108,17 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E177" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F177" t="s" s="2">
         <v>75</v>
@@ -20130,11 +20136,11 @@
         <v>74</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L177" s="2"/>
       <c r="M177" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N177" s="2"/>
       <c r="O177" s="2"/>
@@ -20143,7 +20149,7 @@
       </c>
       <c r="Q177" s="2"/>
       <c r="R177" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S177" t="s" s="2">
         <v>74</v>
@@ -20185,7 +20191,7 @@
         <v>74</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>80</v>
@@ -20205,21 +20211,23 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E178" s="2"/>
+      <c r="E178" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F178" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G178" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H178" t="s" s="2">
         <v>74</v>
@@ -20231,11 +20239,11 @@
         <v>74</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L178" s="2"/>
       <c r="M178" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
@@ -20286,13 +20294,13 @@
         <v>74</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH178" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI178" t="s" s="2">
         <v>74</v>
@@ -20306,10 +20314,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -20317,10 +20325,10 @@
       </c>
       <c r="E179" s="2"/>
       <c r="F179" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G179" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H179" t="s" s="2">
         <v>74</v>
@@ -20332,10 +20340,12 @@
         <v>74</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L179" s="2"/>
-      <c r="M179" s="2"/>
+      <c r="M179" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N179" s="2"/>
       <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
@@ -20346,7 +20356,7 @@
         <v>74</v>
       </c>
       <c r="S179" t="s" s="2">
-        <v>473</v>
+        <v>74</v>
       </c>
       <c r="T179" t="s" s="2">
         <v>74</v>
@@ -20361,11 +20371,13 @@
         <v>74</v>
       </c>
       <c r="X179" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y179" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y179" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z179" t="s" s="2">
-        <v>474</v>
+        <v>74</v>
       </c>
       <c r="AA179" t="s" s="2">
         <v>74</v>
@@ -20383,13 +20395,13 @@
         <v>74</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>475</v>
+        <v>125</v>
       </c>
       <c r="AG179" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH179" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI179" t="s" s="2">
         <v>74</v>
@@ -20403,10 +20415,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -20414,7 +20426,7 @@
       </c>
       <c r="E180" s="2"/>
       <c r="F180" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G180" t="s" s="2">
         <v>75</v>
@@ -20429,12 +20441,10 @@
         <v>74</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L180" s="2"/>
-      <c r="M180" t="s" s="2">
-        <v>478</v>
-      </c>
+      <c r="M180" s="2"/>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
@@ -20445,7 +20455,7 @@
         <v>74</v>
       </c>
       <c r="S180" t="s" s="2">
-        <v>74</v>
+        <v>476</v>
       </c>
       <c r="T180" t="s" s="2">
         <v>74</v>
@@ -20460,13 +20470,11 @@
         <v>74</v>
       </c>
       <c r="X180" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y180" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y180" s="2"/>
       <c r="Z180" t="s" s="2">
-        <v>74</v>
+        <v>477</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>74</v>
@@ -20484,10 +20492,10 @@
         <v>74</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AG180" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH180" t="s" s="2">
         <v>75</v>
@@ -20504,10 +20512,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -20534,12 +20542,12 @@
       </c>
       <c r="L181" s="2"/>
       <c r="M181" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
-        <v>483</v>
+        <v>74</v>
       </c>
       <c r="Q181" s="2"/>
       <c r="R181" t="s" s="2">
@@ -20585,7 +20593,7 @@
         <v>74</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>80</v>
@@ -20605,10 +20613,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -20634,11 +20642,13 @@
         <v>107</v>
       </c>
       <c r="L182" s="2"/>
-      <c r="M182" s="2"/>
+      <c r="M182" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="N182" s="2"/>
       <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
-        <v>74</v>
+        <v>486</v>
       </c>
       <c r="Q182" s="2"/>
       <c r="R182" t="s" s="2">
@@ -20704,7 +20714,7 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>489</v>
@@ -20730,7 +20740,7 @@
         <v>74</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>490</v>
+        <v>107</v>
       </c>
       <c r="L183" s="2"/>
       <c r="M183" s="2"/>
@@ -20783,7 +20793,7 @@
         <v>74</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>80</v>
@@ -20803,10 +20813,10 @@
     </row>
     <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -20829,7 +20839,7 @@
         <v>74</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>224</v>
+        <v>493</v>
       </c>
       <c r="L184" s="2"/>
       <c r="M184" s="2"/>
@@ -20902,7 +20912,7 @@
     </row>
     <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>496</v>
@@ -20928,7 +20938,7 @@
         <v>74</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>497</v>
+        <v>225</v>
       </c>
       <c r="L185" s="2"/>
       <c r="M185" s="2"/>
@@ -20981,7 +20991,7 @@
         <v>74</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>80</v>
@@ -21001,10 +21011,10 @@
     </row>
     <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -21027,7 +21037,7 @@
         <v>74</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="L186" s="2"/>
       <c r="M186" s="2"/>
@@ -21080,7 +21090,7 @@
         <v>74</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>80</v>
@@ -21100,10 +21110,10 @@
     </row>
     <row r="187" hidden="true">
       <c r="A187" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C187" s="2"/>
       <c r="D187" t="s" s="2">
@@ -21126,7 +21136,7 @@
         <v>74</v>
       </c>
       <c r="K187" t="s" s="2">
-        <v>552</v>
+        <v>504</v>
       </c>
       <c r="L187" s="2"/>
       <c r="M187" s="2"/>
@@ -21179,7 +21189,7 @@
         <v>74</v>
       </c>
       <c r="AF187" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG187" t="s" s="2">
         <v>80</v>
@@ -21199,10 +21209,10 @@
     </row>
     <row r="188" hidden="true">
       <c r="A188" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C188" s="2"/>
       <c r="D188" t="s" s="2">
@@ -21225,7 +21235,7 @@
         <v>74</v>
       </c>
       <c r="K188" t="s" s="2">
-        <v>509</v>
+        <v>555</v>
       </c>
       <c r="L188" s="2"/>
       <c r="M188" s="2"/>
@@ -21278,7 +21288,7 @@
         <v>74</v>
       </c>
       <c r="AF188" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG188" t="s" s="2">
         <v>80</v>
@@ -21298,10 +21308,10 @@
     </row>
     <row r="189" hidden="true">
       <c r="A189" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C189" s="2"/>
       <c r="D189" t="s" s="2">
@@ -21324,7 +21334,7 @@
         <v>74</v>
       </c>
       <c r="K189" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L189" s="2"/>
       <c r="M189" s="2"/>
@@ -21377,7 +21387,7 @@
         <v>74</v>
       </c>
       <c r="AF189" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG189" t="s" s="2">
         <v>80</v>
@@ -21397,10 +21407,10 @@
     </row>
     <row r="190" hidden="true">
       <c r="A190" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C190" s="2"/>
       <c r="D190" t="s" s="2">
@@ -21423,7 +21433,7 @@
         <v>74</v>
       </c>
       <c r="K190" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="L190" s="2"/>
       <c r="M190" s="2"/>
@@ -21476,7 +21486,7 @@
         <v>74</v>
       </c>
       <c r="AF190" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG190" t="s" s="2">
         <v>80</v>
@@ -21496,10 +21506,10 @@
     </row>
     <row r="191" hidden="true">
       <c r="A191" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C191" s="2"/>
       <c r="D191" t="s" s="2">
@@ -21522,7 +21532,7 @@
         <v>74</v>
       </c>
       <c r="K191" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L191" s="2"/>
       <c r="M191" s="2"/>
@@ -21575,7 +21585,7 @@
         <v>74</v>
       </c>
       <c r="AF191" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG191" t="s" s="2">
         <v>80</v>
@@ -21595,10 +21605,10 @@
     </row>
     <row r="192" hidden="true">
       <c r="A192" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C192" s="2"/>
       <c r="D192" t="s" s="2">
@@ -21621,7 +21631,7 @@
         <v>74</v>
       </c>
       <c r="K192" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L192" s="2"/>
       <c r="M192" s="2"/>
@@ -21674,7 +21684,7 @@
         <v>74</v>
       </c>
       <c r="AF192" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG192" t="s" s="2">
         <v>80</v>
@@ -21694,10 +21704,10 @@
     </row>
     <row r="193" hidden="true">
       <c r="A193" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C193" s="2"/>
       <c r="D193" t="s" s="2">
@@ -21720,7 +21730,7 @@
         <v>74</v>
       </c>
       <c r="K193" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L193" s="2"/>
       <c r="M193" s="2"/>
@@ -21773,7 +21783,7 @@
         <v>74</v>
       </c>
       <c r="AF193" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG193" t="s" s="2">
         <v>80</v>
@@ -21793,14 +21803,12 @@
     </row>
     <row r="194" hidden="true">
       <c r="A194" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C194" t="s" s="2">
-        <v>560</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="C194" s="2"/>
       <c r="D194" t="s" s="2">
         <v>74</v>
       </c>
@@ -21821,11 +21829,9 @@
         <v>74</v>
       </c>
       <c r="K194" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="L194" t="s" s="2">
-        <v>561</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="L194" s="2"/>
       <c r="M194" s="2"/>
       <c r="N194" s="2"/>
       <c r="O194" s="2"/>
@@ -21876,13 +21882,13 @@
         <v>74</v>
       </c>
       <c r="AF194" t="s" s="2">
-        <v>447</v>
+        <v>533</v>
       </c>
       <c r="AG194" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH194" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI194" t="s" s="2">
         <v>74</v>
@@ -21899,15 +21905,15 @@
         <v>562</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C195" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="C195" t="s" s="2">
+        <v>563</v>
+      </c>
       <c r="D195" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E195" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E195" s="2"/>
       <c r="F195" t="s" s="2">
         <v>80</v>
       </c>
@@ -21924,12 +21930,12 @@
         <v>74</v>
       </c>
       <c r="K195" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L195" s="2"/>
-      <c r="M195" t="s" s="2">
-        <v>86</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="L195" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="M195" s="2"/>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
       <c r="P195" t="s" s="2">
@@ -21955,11 +21961,13 @@
         <v>74</v>
       </c>
       <c r="X195" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y195" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y195" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z195" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA195" t="s" s="2">
         <v>74</v>
@@ -21977,13 +21985,13 @@
         <v>74</v>
       </c>
       <c r="AF195" t="s" s="2">
-        <v>89</v>
+        <v>450</v>
       </c>
       <c r="AG195" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH195" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI195" t="s" s="2">
         <v>74</v>
@@ -21997,21 +22005,23 @@
     </row>
     <row r="196" hidden="true">
       <c r="A196" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C196" s="2"/>
       <c r="D196" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E196" s="2"/>
+      <c r="E196" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F196" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G196" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H196" t="s" s="2">
         <v>74</v>
@@ -22023,11 +22033,11 @@
         <v>74</v>
       </c>
       <c r="K196" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L196" s="2"/>
       <c r="M196" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -22054,13 +22064,11 @@
         <v>74</v>
       </c>
       <c r="X196" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y196" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y196" s="2"/>
       <c r="Z196" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA196" t="s" s="2">
         <v>74</v>
@@ -22078,13 +22086,13 @@
         <v>74</v>
       </c>
       <c r="AF196" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG196" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH196" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI196" t="s" s="2">
         <v>74</v>
@@ -22098,10 +22106,10 @@
     </row>
     <row r="197" hidden="true">
       <c r="A197" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C197" s="2"/>
       <c r="D197" t="s" s="2">
@@ -22112,7 +22120,7 @@
         <v>80</v>
       </c>
       <c r="G197" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H197" t="s" s="2">
         <v>74</v>
@@ -22124,11 +22132,11 @@
         <v>74</v>
       </c>
       <c r="K197" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L197" s="2"/>
       <c r="M197" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N197" s="2"/>
       <c r="O197" s="2"/>
@@ -22179,19 +22187,19 @@
         <v>74</v>
       </c>
       <c r="AF197" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG197" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH197" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI197" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ197" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK197" t="s" s="2">
         <v>74</v>
@@ -22199,18 +22207,16 @@
     </row>
     <row r="198" hidden="true">
       <c r="A198" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C198" s="2"/>
       <c r="D198" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E198" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E198" s="2"/>
       <c r="F198" t="s" s="2">
         <v>80</v>
       </c>
@@ -22227,11 +22233,11 @@
         <v>74</v>
       </c>
       <c r="K198" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L198" s="2"/>
       <c r="M198" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N198" s="2"/>
       <c r="O198" s="2"/>
@@ -22258,11 +22264,13 @@
         <v>74</v>
       </c>
       <c r="X198" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y198" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y198" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z198" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA198" t="s" s="2">
         <v>74</v>
@@ -22280,7 +22288,7 @@
         <v>74</v>
       </c>
       <c r="AF198" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG198" t="s" s="2">
         <v>80</v>
@@ -22292,7 +22300,7 @@
         <v>74</v>
       </c>
       <c r="AJ198" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK198" t="s" s="2">
         <v>74</v>
@@ -22300,17 +22308,17 @@
     </row>
     <row r="199" hidden="true">
       <c r="A199" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C199" s="2"/>
       <c r="D199" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E199" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F199" t="s" s="2">
         <v>80</v>
@@ -22328,11 +22336,11 @@
         <v>74</v>
       </c>
       <c r="K199" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L199" s="2"/>
       <c r="M199" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N199" s="2"/>
       <c r="O199" s="2"/>
@@ -22359,13 +22367,11 @@
         <v>74</v>
       </c>
       <c r="X199" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y199" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y199" s="2"/>
       <c r="Z199" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA199" t="s" s="2">
         <v>74</v>
@@ -22383,7 +22389,7 @@
         <v>74</v>
       </c>
       <c r="AF199" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG199" t="s" s="2">
         <v>80</v>
@@ -22403,17 +22409,17 @@
     </row>
     <row r="200" hidden="true">
       <c r="A200" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C200" s="2"/>
       <c r="D200" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E200" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F200" t="s" s="2">
         <v>80</v>
@@ -22431,11 +22437,11 @@
         <v>74</v>
       </c>
       <c r="K200" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L200" s="2"/>
       <c r="M200" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N200" s="2"/>
       <c r="O200" s="2"/>
@@ -22486,7 +22492,7 @@
         <v>74</v>
       </c>
       <c r="AF200" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG200" t="s" s="2">
         <v>80</v>
@@ -22506,20 +22512,20 @@
     </row>
     <row r="201" hidden="true">
       <c r="A201" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C201" s="2"/>
       <c r="D201" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E201" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F201" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G201" t="s" s="2">
         <v>75</v>
@@ -22534,11 +22540,11 @@
         <v>74</v>
       </c>
       <c r="K201" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L201" s="2"/>
       <c r="M201" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N201" s="2"/>
       <c r="O201" s="2"/>
@@ -22547,7 +22553,7 @@
       </c>
       <c r="Q201" s="2"/>
       <c r="R201" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S201" t="s" s="2">
         <v>74</v>
@@ -22589,7 +22595,7 @@
         <v>74</v>
       </c>
       <c r="AF201" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG201" t="s" s="2">
         <v>80</v>
@@ -22609,17 +22615,17 @@
     </row>
     <row r="202" hidden="true">
       <c r="A202" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C202" s="2"/>
       <c r="D202" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E202" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F202" t="s" s="2">
         <v>75</v>
@@ -22637,11 +22643,11 @@
         <v>74</v>
       </c>
       <c r="K202" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L202" s="2"/>
       <c r="M202" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N202" s="2"/>
       <c r="O202" s="2"/>
@@ -22650,7 +22656,7 @@
       </c>
       <c r="Q202" s="2"/>
       <c r="R202" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S202" t="s" s="2">
         <v>74</v>
@@ -22692,7 +22698,7 @@
         <v>74</v>
       </c>
       <c r="AF202" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG202" t="s" s="2">
         <v>80</v>
@@ -22712,21 +22718,23 @@
     </row>
     <row r="203" hidden="true">
       <c r="A203" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C203" s="2"/>
       <c r="D203" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E203" s="2"/>
+      <c r="E203" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F203" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G203" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H203" t="s" s="2">
         <v>74</v>
@@ -22738,11 +22746,11 @@
         <v>74</v>
       </c>
       <c r="K203" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L203" s="2"/>
       <c r="M203" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N203" s="2"/>
       <c r="O203" s="2"/>
@@ -22793,13 +22801,13 @@
         <v>74</v>
       </c>
       <c r="AF203" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG203" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH203" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI203" t="s" s="2">
         <v>74</v>
@@ -22813,10 +22821,10 @@
     </row>
     <row r="204" hidden="true">
       <c r="A204" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C204" s="2"/>
       <c r="D204" t="s" s="2">
@@ -22824,10 +22832,10 @@
       </c>
       <c r="E204" s="2"/>
       <c r="F204" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G204" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H204" t="s" s="2">
         <v>74</v>
@@ -22839,10 +22847,12 @@
         <v>74</v>
       </c>
       <c r="K204" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L204" s="2"/>
-      <c r="M204" s="2"/>
+      <c r="M204" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N204" s="2"/>
       <c r="O204" s="2"/>
       <c r="P204" t="s" s="2">
@@ -22853,7 +22863,7 @@
         <v>74</v>
       </c>
       <c r="S204" t="s" s="2">
-        <v>473</v>
+        <v>74</v>
       </c>
       <c r="T204" t="s" s="2">
         <v>74</v>
@@ -22868,11 +22878,13 @@
         <v>74</v>
       </c>
       <c r="X204" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y204" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y204" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z204" t="s" s="2">
-        <v>474</v>
+        <v>74</v>
       </c>
       <c r="AA204" t="s" s="2">
         <v>74</v>
@@ -22890,13 +22902,13 @@
         <v>74</v>
       </c>
       <c r="AF204" t="s" s="2">
-        <v>475</v>
+        <v>125</v>
       </c>
       <c r="AG204" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH204" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI204" t="s" s="2">
         <v>74</v>
@@ -22910,10 +22922,10 @@
     </row>
     <row r="205" hidden="true">
       <c r="A205" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C205" s="2"/>
       <c r="D205" t="s" s="2">
@@ -22921,7 +22933,7 @@
       </c>
       <c r="E205" s="2"/>
       <c r="F205" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G205" t="s" s="2">
         <v>75</v>
@@ -22936,12 +22948,10 @@
         <v>74</v>
       </c>
       <c r="K205" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L205" s="2"/>
-      <c r="M205" t="s" s="2">
-        <v>478</v>
-      </c>
+      <c r="M205" s="2"/>
       <c r="N205" s="2"/>
       <c r="O205" s="2"/>
       <c r="P205" t="s" s="2">
@@ -22952,7 +22962,7 @@
         <v>74</v>
       </c>
       <c r="S205" t="s" s="2">
-        <v>74</v>
+        <v>476</v>
       </c>
       <c r="T205" t="s" s="2">
         <v>74</v>
@@ -22967,13 +22977,11 @@
         <v>74</v>
       </c>
       <c r="X205" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y205" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y205" s="2"/>
       <c r="Z205" t="s" s="2">
-        <v>74</v>
+        <v>477</v>
       </c>
       <c r="AA205" t="s" s="2">
         <v>74</v>
@@ -22991,10 +22999,10 @@
         <v>74</v>
       </c>
       <c r="AF205" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AG205" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH205" t="s" s="2">
         <v>75</v>
@@ -23011,10 +23019,10 @@
     </row>
     <row r="206" hidden="true">
       <c r="A206" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C206" s="2"/>
       <c r="D206" t="s" s="2">
@@ -23041,12 +23049,12 @@
       </c>
       <c r="L206" s="2"/>
       <c r="M206" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="N206" s="2"/>
       <c r="O206" s="2"/>
       <c r="P206" t="s" s="2">
-        <v>483</v>
+        <v>74</v>
       </c>
       <c r="Q206" s="2"/>
       <c r="R206" t="s" s="2">
@@ -23092,7 +23100,7 @@
         <v>74</v>
       </c>
       <c r="AF206" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AG206" t="s" s="2">
         <v>80</v>
@@ -23112,10 +23120,10 @@
     </row>
     <row r="207" hidden="true">
       <c r="A207" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C207" s="2"/>
       <c r="D207" t="s" s="2">
@@ -23141,11 +23149,13 @@
         <v>107</v>
       </c>
       <c r="L207" s="2"/>
-      <c r="M207" s="2"/>
+      <c r="M207" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="N207" s="2"/>
       <c r="O207" s="2"/>
       <c r="P207" t="s" s="2">
-        <v>74</v>
+        <v>486</v>
       </c>
       <c r="Q207" s="2"/>
       <c r="R207" t="s" s="2">
@@ -23211,7 +23221,7 @@
     </row>
     <row r="208" hidden="true">
       <c r="A208" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B208" t="s" s="2">
         <v>489</v>
@@ -23237,7 +23247,7 @@
         <v>74</v>
       </c>
       <c r="K208" t="s" s="2">
-        <v>490</v>
+        <v>107</v>
       </c>
       <c r="L208" s="2"/>
       <c r="M208" s="2"/>
@@ -23290,7 +23300,7 @@
         <v>74</v>
       </c>
       <c r="AF208" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AG208" t="s" s="2">
         <v>80</v>
@@ -23310,10 +23320,10 @@
     </row>
     <row r="209" hidden="true">
       <c r="A209" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C209" s="2"/>
       <c r="D209" t="s" s="2">
@@ -23336,7 +23346,7 @@
         <v>74</v>
       </c>
       <c r="K209" t="s" s="2">
-        <v>224</v>
+        <v>493</v>
       </c>
       <c r="L209" s="2"/>
       <c r="M209" s="2"/>
@@ -23409,7 +23419,7 @@
     </row>
     <row r="210" hidden="true">
       <c r="A210" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B210" t="s" s="2">
         <v>496</v>
@@ -23435,7 +23445,7 @@
         <v>74</v>
       </c>
       <c r="K210" t="s" s="2">
-        <v>497</v>
+        <v>225</v>
       </c>
       <c r="L210" s="2"/>
       <c r="M210" s="2"/>
@@ -23488,7 +23498,7 @@
         <v>74</v>
       </c>
       <c r="AF210" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AG210" t="s" s="2">
         <v>80</v>
@@ -23508,10 +23518,10 @@
     </row>
     <row r="211" hidden="true">
       <c r="A211" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C211" s="2"/>
       <c r="D211" t="s" s="2">
@@ -23534,7 +23544,7 @@
         <v>74</v>
       </c>
       <c r="K211" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="L211" s="2"/>
       <c r="M211" s="2"/>
@@ -23587,7 +23597,7 @@
         <v>74</v>
       </c>
       <c r="AF211" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG211" t="s" s="2">
         <v>80</v>
@@ -23607,10 +23617,10 @@
     </row>
     <row r="212" hidden="true">
       <c r="A212" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C212" s="2"/>
       <c r="D212" t="s" s="2">
@@ -23633,7 +23643,7 @@
         <v>74</v>
       </c>
       <c r="K212" t="s" s="2">
-        <v>580</v>
+        <v>504</v>
       </c>
       <c r="L212" s="2"/>
       <c r="M212" s="2"/>
@@ -23686,7 +23696,7 @@
         <v>74</v>
       </c>
       <c r="AF212" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG212" t="s" s="2">
         <v>80</v>
@@ -23706,10 +23716,10 @@
     </row>
     <row r="213" hidden="true">
       <c r="A213" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C213" s="2"/>
       <c r="D213" t="s" s="2">
@@ -23732,7 +23742,7 @@
         <v>74</v>
       </c>
       <c r="K213" t="s" s="2">
-        <v>509</v>
+        <v>583</v>
       </c>
       <c r="L213" s="2"/>
       <c r="M213" s="2"/>
@@ -23785,7 +23795,7 @@
         <v>74</v>
       </c>
       <c r="AF213" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG213" t="s" s="2">
         <v>80</v>
@@ -23805,10 +23815,10 @@
     </row>
     <row r="214" hidden="true">
       <c r="A214" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C214" s="2"/>
       <c r="D214" t="s" s="2">
@@ -23831,7 +23841,7 @@
         <v>74</v>
       </c>
       <c r="K214" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L214" s="2"/>
       <c r="M214" s="2"/>
@@ -23884,7 +23894,7 @@
         <v>74</v>
       </c>
       <c r="AF214" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG214" t="s" s="2">
         <v>80</v>
@@ -23904,10 +23914,10 @@
     </row>
     <row r="215" hidden="true">
       <c r="A215" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C215" s="2"/>
       <c r="D215" t="s" s="2">
@@ -23930,7 +23940,7 @@
         <v>74</v>
       </c>
       <c r="K215" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="L215" s="2"/>
       <c r="M215" s="2"/>
@@ -23983,7 +23993,7 @@
         <v>74</v>
       </c>
       <c r="AF215" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG215" t="s" s="2">
         <v>80</v>
@@ -24003,10 +24013,10 @@
     </row>
     <row r="216" hidden="true">
       <c r="A216" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C216" s="2"/>
       <c r="D216" t="s" s="2">
@@ -24029,7 +24039,7 @@
         <v>74</v>
       </c>
       <c r="K216" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L216" s="2"/>
       <c r="M216" s="2"/>
@@ -24082,7 +24092,7 @@
         <v>74</v>
       </c>
       <c r="AF216" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG216" t="s" s="2">
         <v>80</v>
@@ -24102,10 +24112,10 @@
     </row>
     <row r="217" hidden="true">
       <c r="A217" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C217" s="2"/>
       <c r="D217" t="s" s="2">
@@ -24128,7 +24138,7 @@
         <v>74</v>
       </c>
       <c r="K217" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L217" s="2"/>
       <c r="M217" s="2"/>
@@ -24181,7 +24191,7 @@
         <v>74</v>
       </c>
       <c r="AF217" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG217" t="s" s="2">
         <v>80</v>
@@ -24201,10 +24211,10 @@
     </row>
     <row r="218" hidden="true">
       <c r="A218" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C218" s="2"/>
       <c r="D218" t="s" s="2">
@@ -24227,7 +24237,7 @@
         <v>74</v>
       </c>
       <c r="K218" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L218" s="2"/>
       <c r="M218" s="2"/>
@@ -24280,7 +24290,7 @@
         <v>74</v>
       </c>
       <c r="AF218" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG218" t="s" s="2">
         <v>80</v>
@@ -24300,14 +24310,12 @@
     </row>
     <row r="219" hidden="true">
       <c r="A219" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="C219" t="s" s="2">
-        <v>588</v>
-      </c>
+        <v>531</v>
+      </c>
+      <c r="C219" s="2"/>
       <c r="D219" t="s" s="2">
         <v>74</v>
       </c>
@@ -24328,11 +24336,9 @@
         <v>74</v>
       </c>
       <c r="K219" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="L219" t="s" s="2">
-        <v>589</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="L219" s="2"/>
       <c r="M219" s="2"/>
       <c r="N219" s="2"/>
       <c r="O219" s="2"/>
@@ -24383,13 +24389,13 @@
         <v>74</v>
       </c>
       <c r="AF219" t="s" s="2">
-        <v>447</v>
+        <v>533</v>
       </c>
       <c r="AG219" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH219" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI219" t="s" s="2">
         <v>74</v>
@@ -24406,15 +24412,15 @@
         <v>590</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="C220" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="C220" t="s" s="2">
+        <v>591</v>
+      </c>
       <c r="D220" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E220" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E220" s="2"/>
       <c r="F220" t="s" s="2">
         <v>80</v>
       </c>
@@ -24431,12 +24437,12 @@
         <v>74</v>
       </c>
       <c r="K220" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L220" s="2"/>
-      <c r="M220" t="s" s="2">
-        <v>86</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="L220" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="M220" s="2"/>
       <c r="N220" s="2"/>
       <c r="O220" s="2"/>
       <c r="P220" t="s" s="2">
@@ -24462,11 +24468,13 @@
         <v>74</v>
       </c>
       <c r="X220" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y220" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y220" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z220" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA220" t="s" s="2">
         <v>74</v>
@@ -24484,13 +24492,13 @@
         <v>74</v>
       </c>
       <c r="AF220" t="s" s="2">
-        <v>89</v>
+        <v>450</v>
       </c>
       <c r="AG220" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH220" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI220" t="s" s="2">
         <v>74</v>
@@ -24504,21 +24512,23 @@
     </row>
     <row r="221" hidden="true">
       <c r="A221" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C221" s="2"/>
       <c r="D221" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E221" s="2"/>
+      <c r="E221" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F221" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G221" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H221" t="s" s="2">
         <v>74</v>
@@ -24530,11 +24540,11 @@
         <v>74</v>
       </c>
       <c r="K221" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="L221" s="2"/>
       <c r="M221" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N221" s="2"/>
       <c r="O221" s="2"/>
@@ -24561,13 +24571,11 @@
         <v>74</v>
       </c>
       <c r="X221" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y221" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y221" s="2"/>
       <c r="Z221" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA221" t="s" s="2">
         <v>74</v>
@@ -24585,13 +24593,13 @@
         <v>74</v>
       </c>
       <c r="AF221" t="s" s="2">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AG221" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH221" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI221" t="s" s="2">
         <v>74</v>
@@ -24605,10 +24613,10 @@
     </row>
     <row r="222" hidden="true">
       <c r="A222" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C222" s="2"/>
       <c r="D222" t="s" s="2">
@@ -24619,7 +24627,7 @@
         <v>80</v>
       </c>
       <c r="G222" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H222" t="s" s="2">
         <v>74</v>
@@ -24631,11 +24639,11 @@
         <v>74</v>
       </c>
       <c r="K222" t="s" s="2">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="L222" s="2"/>
       <c r="M222" t="s" s="2">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="N222" s="2"/>
       <c r="O222" s="2"/>
@@ -24686,19 +24694,19 @@
         <v>74</v>
       </c>
       <c r="AF222" t="s" s="2">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AG222" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH222" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI222" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AJ222" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK222" t="s" s="2">
         <v>74</v>
@@ -24706,18 +24714,16 @@
     </row>
     <row r="223" hidden="true">
       <c r="A223" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C223" s="2"/>
       <c r="D223" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E223" t="s" s="2">
-        <v>84</v>
-      </c>
+      <c r="E223" s="2"/>
       <c r="F223" t="s" s="2">
         <v>80</v>
       </c>
@@ -24734,11 +24740,11 @@
         <v>74</v>
       </c>
       <c r="K223" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L223" s="2"/>
       <c r="M223" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="N223" s="2"/>
       <c r="O223" s="2"/>
@@ -24765,11 +24771,13 @@
         <v>74</v>
       </c>
       <c r="X223" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y223" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y223" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z223" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA223" t="s" s="2">
         <v>74</v>
@@ -24787,7 +24795,7 @@
         <v>74</v>
       </c>
       <c r="AF223" t="s" s="2">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="AG223" t="s" s="2">
         <v>80</v>
@@ -24799,7 +24807,7 @@
         <v>74</v>
       </c>
       <c r="AJ223" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK223" t="s" s="2">
         <v>74</v>
@@ -24807,17 +24815,17 @@
     </row>
     <row r="224" hidden="true">
       <c r="A224" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C224" s="2"/>
       <c r="D224" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E224" t="s" s="2">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="F224" t="s" s="2">
         <v>80</v>
@@ -24835,11 +24843,11 @@
         <v>74</v>
       </c>
       <c r="K224" t="s" s="2">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="L224" s="2"/>
       <c r="M224" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="N224" s="2"/>
       <c r="O224" s="2"/>
@@ -24866,13 +24874,11 @@
         <v>74</v>
       </c>
       <c r="X224" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y224" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y224" s="2"/>
       <c r="Z224" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA224" t="s" s="2">
         <v>74</v>
@@ -24890,7 +24896,7 @@
         <v>74</v>
       </c>
       <c r="AF224" t="s" s="2">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="AG224" t="s" s="2">
         <v>80</v>
@@ -24910,17 +24916,17 @@
     </row>
     <row r="225" hidden="true">
       <c r="A225" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C225" s="2"/>
       <c r="D225" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E225" t="s" s="2">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="F225" t="s" s="2">
         <v>80</v>
@@ -24938,11 +24944,11 @@
         <v>74</v>
       </c>
       <c r="K225" t="s" s="2">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="L225" s="2"/>
       <c r="M225" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="N225" s="2"/>
       <c r="O225" s="2"/>
@@ -24993,7 +24999,7 @@
         <v>74</v>
       </c>
       <c r="AF225" t="s" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="AG225" t="s" s="2">
         <v>80</v>
@@ -25013,20 +25019,20 @@
     </row>
     <row r="226" hidden="true">
       <c r="A226" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C226" s="2"/>
       <c r="D226" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E226" t="s" s="2">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="F226" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G226" t="s" s="2">
         <v>75</v>
@@ -25041,11 +25047,11 @@
         <v>74</v>
       </c>
       <c r="K226" t="s" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="L226" s="2"/>
       <c r="M226" t="s" s="2">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="N226" s="2"/>
       <c r="O226" s="2"/>
@@ -25054,7 +25060,7 @@
       </c>
       <c r="Q226" s="2"/>
       <c r="R226" t="s" s="2">
-        <v>114</v>
+        <v>74</v>
       </c>
       <c r="S226" t="s" s="2">
         <v>74</v>
@@ -25096,7 +25102,7 @@
         <v>74</v>
       </c>
       <c r="AF226" t="s" s="2">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="AG226" t="s" s="2">
         <v>80</v>
@@ -25116,17 +25122,17 @@
     </row>
     <row r="227" hidden="true">
       <c r="A227" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C227" s="2"/>
       <c r="D227" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E227" t="s" s="2">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="F227" t="s" s="2">
         <v>75</v>
@@ -25144,11 +25150,11 @@
         <v>74</v>
       </c>
       <c r="K227" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L227" s="2"/>
       <c r="M227" t="s" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="N227" s="2"/>
       <c r="O227" s="2"/>
@@ -25157,7 +25163,7 @@
       </c>
       <c r="Q227" s="2"/>
       <c r="R227" t="s" s="2">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="S227" t="s" s="2">
         <v>74</v>
@@ -25199,7 +25205,7 @@
         <v>74</v>
       </c>
       <c r="AF227" t="s" s="2">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AG227" t="s" s="2">
         <v>80</v>
@@ -25219,21 +25225,23 @@
     </row>
     <row r="228" hidden="true">
       <c r="A228" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C228" s="2"/>
       <c r="D228" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E228" s="2"/>
+      <c r="E228" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="F228" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G228" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H228" t="s" s="2">
         <v>74</v>
@@ -25245,11 +25253,11 @@
         <v>74</v>
       </c>
       <c r="K228" t="s" s="2">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="L228" s="2"/>
       <c r="M228" t="s" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="N228" s="2"/>
       <c r="O228" s="2"/>
@@ -25300,13 +25308,13 @@
         <v>74</v>
       </c>
       <c r="AF228" t="s" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH228" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI228" t="s" s="2">
         <v>74</v>
@@ -25320,10 +25328,10 @@
     </row>
     <row r="229" hidden="true">
       <c r="A229" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C229" s="2"/>
       <c r="D229" t="s" s="2">
@@ -25331,10 +25339,10 @@
       </c>
       <c r="E229" s="2"/>
       <c r="F229" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G229" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H229" t="s" s="2">
         <v>74</v>
@@ -25346,10 +25354,12 @@
         <v>74</v>
       </c>
       <c r="K229" t="s" s="2">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="L229" s="2"/>
-      <c r="M229" s="2"/>
+      <c r="M229" t="s" s="2">
+        <v>122</v>
+      </c>
       <c r="N229" s="2"/>
       <c r="O229" s="2"/>
       <c r="P229" t="s" s="2">
@@ -25360,7 +25370,7 @@
         <v>74</v>
       </c>
       <c r="S229" t="s" s="2">
-        <v>473</v>
+        <v>74</v>
       </c>
       <c r="T229" t="s" s="2">
         <v>74</v>
@@ -25375,11 +25385,13 @@
         <v>74</v>
       </c>
       <c r="X229" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y229" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y229" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z229" t="s" s="2">
-        <v>474</v>
+        <v>74</v>
       </c>
       <c r="AA229" t="s" s="2">
         <v>74</v>
@@ -25397,13 +25409,13 @@
         <v>74</v>
       </c>
       <c r="AF229" t="s" s="2">
-        <v>475</v>
+        <v>125</v>
       </c>
       <c r="AG229" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH229" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI229" t="s" s="2">
         <v>74</v>
@@ -25417,10 +25429,10 @@
     </row>
     <row r="230" hidden="true">
       <c r="A230" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C230" s="2"/>
       <c r="D230" t="s" s="2">
@@ -25428,7 +25440,7 @@
       </c>
       <c r="E230" s="2"/>
       <c r="F230" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G230" t="s" s="2">
         <v>75</v>
@@ -25443,12 +25455,10 @@
         <v>74</v>
       </c>
       <c r="K230" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="L230" s="2"/>
-      <c r="M230" t="s" s="2">
-        <v>478</v>
-      </c>
+      <c r="M230" s="2"/>
       <c r="N230" s="2"/>
       <c r="O230" s="2"/>
       <c r="P230" t="s" s="2">
@@ -25459,7 +25469,7 @@
         <v>74</v>
       </c>
       <c r="S230" t="s" s="2">
-        <v>74</v>
+        <v>476</v>
       </c>
       <c r="T230" t="s" s="2">
         <v>74</v>
@@ -25474,13 +25484,11 @@
         <v>74</v>
       </c>
       <c r="X230" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y230" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y230" s="2"/>
       <c r="Z230" t="s" s="2">
-        <v>74</v>
+        <v>477</v>
       </c>
       <c r="AA230" t="s" s="2">
         <v>74</v>
@@ -25498,10 +25506,10 @@
         <v>74</v>
       </c>
       <c r="AF230" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AG230" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AH230" t="s" s="2">
         <v>75</v>
@@ -25518,10 +25526,10 @@
     </row>
     <row r="231" hidden="true">
       <c r="A231" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C231" s="2"/>
       <c r="D231" t="s" s="2">
@@ -25548,12 +25556,12 @@
       </c>
       <c r="L231" s="2"/>
       <c r="M231" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="N231" s="2"/>
       <c r="O231" s="2"/>
       <c r="P231" t="s" s="2">
-        <v>483</v>
+        <v>74</v>
       </c>
       <c r="Q231" s="2"/>
       <c r="R231" t="s" s="2">
@@ -25599,7 +25607,7 @@
         <v>74</v>
       </c>
       <c r="AF231" t="s" s="2">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="AG231" t="s" s="2">
         <v>80</v>
@@ -25619,10 +25627,10 @@
     </row>
     <row r="232" hidden="true">
       <c r="A232" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C232" s="2"/>
       <c r="D232" t="s" s="2">
@@ -25648,11 +25656,13 @@
         <v>107</v>
       </c>
       <c r="L232" s="2"/>
-      <c r="M232" s="2"/>
+      <c r="M232" t="s" s="2">
+        <v>485</v>
+      </c>
       <c r="N232" s="2"/>
       <c r="O232" s="2"/>
       <c r="P232" t="s" s="2">
-        <v>74</v>
+        <v>486</v>
       </c>
       <c r="Q232" s="2"/>
       <c r="R232" t="s" s="2">
@@ -25718,7 +25728,7 @@
     </row>
     <row r="233" hidden="true">
       <c r="A233" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B233" t="s" s="2">
         <v>489</v>
@@ -25744,7 +25754,7 @@
         <v>74</v>
       </c>
       <c r="K233" t="s" s="2">
-        <v>490</v>
+        <v>107</v>
       </c>
       <c r="L233" s="2"/>
       <c r="M233" s="2"/>
@@ -25797,7 +25807,7 @@
         <v>74</v>
       </c>
       <c r="AF233" t="s" s="2">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="AG233" t="s" s="2">
         <v>80</v>
@@ -25817,10 +25827,10 @@
     </row>
     <row r="234" hidden="true">
       <c r="A234" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C234" s="2"/>
       <c r="D234" t="s" s="2">
@@ -25843,7 +25853,7 @@
         <v>74</v>
       </c>
       <c r="K234" t="s" s="2">
-        <v>224</v>
+        <v>493</v>
       </c>
       <c r="L234" s="2"/>
       <c r="M234" s="2"/>
@@ -25916,7 +25926,7 @@
     </row>
     <row r="235" hidden="true">
       <c r="A235" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B235" t="s" s="2">
         <v>496</v>
@@ -25942,7 +25952,7 @@
         <v>74</v>
       </c>
       <c r="K235" t="s" s="2">
-        <v>497</v>
+        <v>225</v>
       </c>
       <c r="L235" s="2"/>
       <c r="M235" s="2"/>
@@ -25995,7 +26005,7 @@
         <v>74</v>
       </c>
       <c r="AF235" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="AG235" t="s" s="2">
         <v>80</v>
@@ -26015,10 +26025,10 @@
     </row>
     <row r="236" hidden="true">
       <c r="A236" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C236" s="2"/>
       <c r="D236" t="s" s="2">
@@ -26041,7 +26051,7 @@
         <v>74</v>
       </c>
       <c r="K236" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="L236" s="2"/>
       <c r="M236" s="2"/>
@@ -26094,7 +26104,7 @@
         <v>74</v>
       </c>
       <c r="AF236" t="s" s="2">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="AG236" t="s" s="2">
         <v>80</v>
@@ -26114,10 +26124,10 @@
     </row>
     <row r="237" hidden="true">
       <c r="A237" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C237" s="2"/>
       <c r="D237" t="s" s="2">
@@ -26140,7 +26150,7 @@
         <v>74</v>
       </c>
       <c r="K237" t="s" s="2">
-        <v>608</v>
+        <v>504</v>
       </c>
       <c r="L237" s="2"/>
       <c r="M237" s="2"/>
@@ -26193,7 +26203,7 @@
         <v>74</v>
       </c>
       <c r="AF237" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AG237" t="s" s="2">
         <v>80</v>
@@ -26213,10 +26223,10 @@
     </row>
     <row r="238" hidden="true">
       <c r="A238" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="C238" s="2"/>
       <c r="D238" t="s" s="2">
@@ -26239,7 +26249,7 @@
         <v>74</v>
       </c>
       <c r="K238" t="s" s="2">
-        <v>509</v>
+        <v>611</v>
       </c>
       <c r="L238" s="2"/>
       <c r="M238" s="2"/>
@@ -26292,7 +26302,7 @@
         <v>74</v>
       </c>
       <c r="AF238" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AG238" t="s" s="2">
         <v>80</v>
@@ -26312,10 +26322,10 @@
     </row>
     <row r="239" hidden="true">
       <c r="A239" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C239" s="2"/>
       <c r="D239" t="s" s="2">
@@ -26338,7 +26348,7 @@
         <v>74</v>
       </c>
       <c r="K239" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="L239" s="2"/>
       <c r="M239" s="2"/>
@@ -26391,7 +26401,7 @@
         <v>74</v>
       </c>
       <c r="AF239" t="s" s="2">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="AG239" t="s" s="2">
         <v>80</v>
@@ -26411,10 +26421,10 @@
     </row>
     <row r="240" hidden="true">
       <c r="A240" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C240" s="2"/>
       <c r="D240" t="s" s="2">
@@ -26437,7 +26447,7 @@
         <v>74</v>
       </c>
       <c r="K240" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="L240" s="2"/>
       <c r="M240" s="2"/>
@@ -26490,7 +26500,7 @@
         <v>74</v>
       </c>
       <c r="AF240" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="AG240" t="s" s="2">
         <v>80</v>
@@ -26510,10 +26520,10 @@
     </row>
     <row r="241" hidden="true">
       <c r="A241" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C241" s="2"/>
       <c r="D241" t="s" s="2">
@@ -26536,7 +26546,7 @@
         <v>74</v>
       </c>
       <c r="K241" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L241" s="2"/>
       <c r="M241" s="2"/>
@@ -26589,7 +26599,7 @@
         <v>74</v>
       </c>
       <c r="AF241" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG241" t="s" s="2">
         <v>80</v>
@@ -26609,10 +26619,10 @@
     </row>
     <row r="242" hidden="true">
       <c r="A242" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C242" s="2"/>
       <c r="D242" t="s" s="2">
@@ -26635,7 +26645,7 @@
         <v>74</v>
       </c>
       <c r="K242" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L242" s="2"/>
       <c r="M242" s="2"/>
@@ -26688,7 +26698,7 @@
         <v>74</v>
       </c>
       <c r="AF242" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AG242" t="s" s="2">
         <v>80</v>
@@ -26708,10 +26718,10 @@
     </row>
     <row r="243" hidden="true">
       <c r="A243" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C243" s="2"/>
       <c r="D243" t="s" s="2">
@@ -26734,7 +26744,7 @@
         <v>74</v>
       </c>
       <c r="K243" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="L243" s="2"/>
       <c r="M243" s="2"/>
@@ -26787,7 +26797,7 @@
         <v>74</v>
       </c>
       <c r="AF243" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>80</v>
@@ -26807,10 +26817,10 @@
     </row>
     <row r="244" hidden="true">
       <c r="A244" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>615</v>
+        <v>531</v>
       </c>
       <c r="C244" s="2"/>
       <c r="D244" t="s" s="2">
@@ -26821,7 +26831,7 @@
         <v>80</v>
       </c>
       <c r="G244" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H244" t="s" s="2">
         <v>74</v>
@@ -26833,7 +26843,7 @@
         <v>74</v>
       </c>
       <c r="K244" t="s" s="2">
-        <v>616</v>
+        <v>532</v>
       </c>
       <c r="L244" s="2"/>
       <c r="M244" s="2"/>
@@ -26886,13 +26896,13 @@
         <v>74</v>
       </c>
       <c r="AF244" t="s" s="2">
-        <v>615</v>
+        <v>533</v>
       </c>
       <c r="AG244" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH244" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI244" t="s" s="2">
         <v>74</v>
@@ -26906,10 +26916,10 @@
     </row>
     <row r="245" hidden="true">
       <c r="A245" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C245" s="2"/>
       <c r="D245" t="s" s="2">
@@ -26932,7 +26942,7 @@
         <v>74</v>
       </c>
       <c r="K245" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L245" s="2"/>
       <c r="M245" s="2"/>
@@ -26985,7 +26995,7 @@
         <v>74</v>
       </c>
       <c r="AF245" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG245" t="s" s="2">
         <v>80</v>
@@ -27005,10 +27015,10 @@
     </row>
     <row r="246" hidden="true">
       <c r="A246" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C246" s="2"/>
       <c r="D246" t="s" s="2">
@@ -27031,7 +27041,7 @@
         <v>74</v>
       </c>
       <c r="K246" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="L246" s="2"/>
       <c r="M246" s="2"/>
@@ -27084,7 +27094,7 @@
         <v>74</v>
       </c>
       <c r="AF246" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AG246" t="s" s="2">
         <v>80</v>
@@ -27102,8 +27112,107 @@
         <v>74</v>
       </c>
     </row>
+    <row r="247" hidden="true">
+      <c r="A247" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="B247" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C247" s="2"/>
+      <c r="D247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E247" s="2"/>
+      <c r="F247" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G247" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K247" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="L247" s="2"/>
+      <c r="M247" s="2"/>
+      <c r="N247" s="2"/>
+      <c r="O247" s="2"/>
+      <c r="P247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q247" s="2"/>
+      <c r="R247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF247" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AG247" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH247" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ247" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK247" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AK246">
+  <autoFilter ref="A1:AK247">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -27113,7 +27222,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI245">
+  <conditionalFormatting sqref="A2:AI246">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T14:20:03+00:00</t>
+    <t>2026-06-29T15:28:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T15:28:29+00:00</t>
+    <t>2026-06-30T08:01:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T08:01:58+00:00</t>
+    <t>2026-06-30T09:01:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:01:37+00:00</t>
+    <t>2026-06-30T09:56:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dispositif-medical.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T09:56:22+00:00</t>
+    <t>2026-08-06T11:33:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
